--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_ARRAIAL_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_ARRAIAL_pgto_05-10-2026.xlsx
@@ -2131,9 +2131,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15">
-        <f> COMISSÃO TOTAL</f>
-        <v/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>COMISSÃO TOTAL (soma)</t>
+        </is>
       </c>
       <c r="B11" s="20">
         <f>SUM(B9:B10)</f>
@@ -2219,9 +2220,10 @@
         <f>SUM(B12:I12)</f>
         <v/>
       </c>
-      <c r="K12" s="30">
-        <f> (comissão total + horas extras) × (4 domingos + feriado 07/09) ÷ 25 dias úteis de setembro/2026.</f>
-        <v/>
+      <c r="K12" s="30" t="inlineStr">
+        <is>
+          <t>Cálculo: (comissão total + horas extras) × (4 domingos + feriado 07/09) ÷ 25 dias úteis de setembro/2026.</t>
+        </is>
       </c>
     </row>
     <row r="13">

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_ARRAIAL_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_ARRAIAL_pgto_05-10-2026.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA SET.26'!$A$4:$J$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE SET.26'!$A$4:$K$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE SET.26'!$A$4:$K$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$203</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'GANHOS DO COLABORADOR'!$A$1:$D$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PONTO SET.26'!$A$4:$I$14</definedName>
@@ -1816,7 +1816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2590,7 +2590,7 @@
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="B24" s="33" t="n"/>
@@ -2961,70 +2961,94 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="B38" s="22" t="inlineStr"/>
+    <row r="37">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
+        </is>
+      </c>
+      <c r="B37" s="28" t="n"/>
+      <c r="C37" s="28" t="n"/>
+      <c r="D37" s="28" t="n"/>
+      <c r="E37" s="28" t="n"/>
+      <c r="F37" s="28" t="n"/>
+      <c r="G37" s="28" t="n"/>
+      <c r="H37" s="28" t="n"/>
+      <c r="I37" s="28" t="n"/>
+      <c r="J37" s="29">
+        <f>SUM(B37:I37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="30" t="inlineStr">
+        <is>
+          <t>Recibo de férias pago fora do holerite — lembrete para o contas a pagar. Preencher se houve férias no mês.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
         <is>
-          <t>Célula amarela, texto azul</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
-        </is>
-      </c>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Célula laranja</t>
+          <t>Célula amarela, texto azul</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
+          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>Texto verde</t>
+          <t>Célula laranja</t>
         </is>
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
+          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
+          <t>Texto verde</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
           <t>Texto preto em célula verde</t>
         </is>
       </c>
-      <c r="B42" s="22" t="inlineStr">
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>resultado de fórmula — não alterar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K36"/>
+  <autoFilter ref="A4:K37"/>
   <mergeCells count="7">
     <mergeCell ref="B41:K41"/>
     <mergeCell ref="B40:K40"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="B43:K43"/>
     <mergeCell ref="B39:K39"/>
-    <mergeCell ref="B38:K38"/>
     <mergeCell ref="B42:K42"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -3427,7 +3451,7 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
@@ -3955,7 +3979,7 @@
       </c>
       <c r="B45" s="27" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
@@ -4483,7 +4507,7 @@
       </c>
       <c r="B70" s="27" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C70" s="27" t="inlineStr">
@@ -5011,7 +5035,7 @@
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C95" s="27" t="inlineStr">
@@ -5539,7 +5563,7 @@
       </c>
       <c r="B120" s="27" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C120" s="27" t="inlineStr">
@@ -6067,7 +6091,7 @@
       </c>
       <c r="B145" s="27" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C145" s="27" t="inlineStr">
@@ -6595,7 +6619,7 @@
       </c>
       <c r="B170" s="27" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C170" s="27" t="inlineStr">
@@ -7123,7 +7147,7 @@
       </c>
       <c r="B195" s="27" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C195" s="27" t="inlineStr">
@@ -7555,7 +7579,7 @@
     <row r="23">
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Adiantamento / vales</t>
+          <t>Adiantamento salarial / vales</t>
         </is>
       </c>
       <c r="C23" s="31">
